--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[(' St', 0.333251953125), ('field', 0.9931640625), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0)]</t>
+          <t>[(' St', 0.333251953125), (',', 1.0), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0)]</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[(' St', 0.333251953125), ('field', 0.9931640625), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.9931640625), (' time', 0.9931640625), (' students', 0.92431640625), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.92431640625), (' visit', 0.9931640625), (' visit', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.9931640625), (' group', 0.99365234375), (' the', 1.0), (' National', 0.9931640625)]</t>
+          <t>[(' St', 0.333251953125), ('.', 1.0), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.9931640625), (' time', 0.9931640625), (' students', 0.92431640625), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.92431640625), (' visit', 0.9931640625), (' visit', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.9931640625), (' group', 0.99365234375), (' the', 1.0), (' National', 0.9931640625)]</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[(' computer', 0.99951171875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99951171875), ('The', 1.0), ('The', 1.0), (' first', 1.0), (' time', 0.9931640625), (' saw', 0.99951171875), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.9931640625), (' to', 1.0), (' meet', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.92431640625), (' group', 0.99951171875), (' the', 1.0), (' International', 0.92431640625), (' Society', 0.92431640625), (' the', 1.0), (' Comput', 0.92431640625)]</t>
+          <t>[(' computer', 0.99951171875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99951171875), ('The', 1.0), ('The', 1.0), (' first', 1.0), (' time', 0.9931640625), (' saw', 0.99951171875), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.9931640625), (' of', 1.0), (' meet', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.92431640625), (' group', 0.99951171875), (' the', 1.0), (' International', 0.92431640625), (' Society', 0.92431640625), (' the', 1.0), (' Comput', 0.92431640625)]</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' a', 0.99755859375), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125)]</t>
+          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' been', 0.55810546875), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125)]</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' a', 0.99755859375), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125), (' good', 1.0), (' place', 1.0), (' to', 1.0), (' ask', 1.0), (' this', 0.99951171875), (',', 0.92431640625), (' is', 0.7490234375), (' is', 0.98046875), (' is', 0.59619140625), (' a', 0.9990234375), (' way', 1.0), (' way', 1.0), (' get', 0.99658203125), (' the', 1.0), (' city', 0.615234375)]</t>
+          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' been', 0.55810546875), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125), (' good', 1.0), (' place', 1.0), (' to', 1.0), (' ask', 1.0), (' this', 0.99951171875), (',', 0.92431640625), (' is', 0.7490234375), (' is', 0.98046875), (' is', 0.59619140625), (' a', 0.9990234375), (' way', 1.0), (' way', 1.0), (' get', 0.99658203125), (' the', 1.0), (' city', 0.615234375)]</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' is', 0.9999998807907104), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398)]</t>
+          <t>[(' The', 0.5), (' I', 0.9964063763618469), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398)]</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' I', 0.9964063763618469), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398), (' British', 0.9241418242454529), (' Alan', 1.0), (' Turing', 1.0), ("'s", 1.0), (' area', 1.0), (' of', 1.0), (' expertise', 1.0), ('?', 0.9999963045120239), (' What', 1.0), (' directors', 1.0), (',', 1.0), (' writers', 1.0), (' and', 1.0), (' more', 1.0), ('.', 1.0)]</t>
+          <t>[(' The', 0.5), (' is', 0.9999998807907104), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398), (' British', 0.9241418242454529), (' Alan', 1.0), (' Turing', 1.0), ("'s", 1.0), (' area', 1.0), (' of', 1.0), (' expertise', 1.0), ('?', 0.9999963045120239), (' What', 1.0), (' directors', 1.0), (',', 1.0), (' writers', 1.0), (' and', 1.0), (' more', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
     </row>
@@ -1366,6 +1366,190 @@
       <c r="F31" t="inlineStr">
         <is>
           <t>[(' What', 0.9964063763618469), (' is', 0.9999994039535522), (' the', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.977022647857666), (' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), ('?\n', 0.9994471669197083), ('Latin', 0.5), (' J', 1.0), ('�', 1.0), ('yl', 1.0), (' t', 0.9999963045120239), (' was', 0.9989677667617798), ('�', 1.0), ('oku', 1.0), (' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Canada.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Simcoe Composite School is located in Simcoe,</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[(' Sim', 0.9999996423721313), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.999841570854187), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>What is the location of Simcoe Composite School?</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Canada.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Simcoe Composite School is located in Simcoe, Ontario, Canada. The school is situated in the heart of Simcoe,</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[(' Sim', 0.9999996423721313), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.999841570854187), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.9933071732521057), (' It', 0.9241418242454529), (' is', 1.0), (' the', 1.0), (' location', 0.9980732202529907), (' high', 0.7772998809814453), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Sim', 0.9241418242454529), ('coe', 1.0), (',', 1.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>musical. What is Alan Turing's area of expertise?</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>logic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>A) Computer Science B) Mathematics C) Physics</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[(' A', 0.9994471669197083), (')', 0.9933071732521057), (' Computer', 0.9999545812606812), (' Science', 0.9999996423721313), (' B', 1.0), (')', 1.0), (' Mathematics', 0.999841570854187), (' C', 1.0), (')', 1.0), (' Physics', 0.9933071732521057)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>musical. What is Alan Turing's area of expertise?</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>25</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>logic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>A) Computer Science B) Mathematics C) Physics D) Biology
+Answer: A) Computer Science
+Explanation: Alan Turing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[(' A', 0.9994471669197083), (')', 0.9933071732521057), (' Computer', 0.9999545812606812), (' Science', 0.9999996423721313), (' B', 1.0), (')', 1.0), (' Mathematics', 0.999841570854187), (' C', 1.0), (')', 1.0), (' Physics', 0.9933071732521057), (' D', 1.0), (')', 1.0), (' Biology', 0.999987006187439), ('\n', 0.999998927116394), ('Answer', 0.9999998807907104), (':', 1.0), (' A', 1.0), (')', 1.0), (' Computer', 1.0), (' Science', 1.0), ('\n', 1.0), ('Explanation', 0.9994471669197083), (':', 1.0), (' Alan', 1.0), (' Turing', 1.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Latin. What is the native language of Louis Jules Trochu?</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>What is the native language of Louis Jules Tro</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[(' Latin', 0.957912266254425), ('.\n', 0.9241418242454529), (' the', 1.0), (' native', 0.977022647857666), (' language', 1.0), (' of', 1.0), (' Louis', 1.0), (' of', 1.0), (' Louis', 1.0), (' Tro', 1.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Latin. What is the native language of Louis Jules Trochu?</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>25</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Latin.
+What is the native language of Louis Jules Trochu? Latin.
+What is the native language of Louis Jules</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[(' Latin', 0.957912266254425), ('.\n', 0.9241418242454529), (' the', 1.0), (' native', 0.977022647857666), (' language', 1.0), (' of', 1.0), (' Louis', 1.0), (' of', 1.0), (' Louis', 1.0), (' Tro', 1.0), ('chu', 1.0), ('?\n', 0.7772998809814453), ('chu', 1.0), ('?', 0.9999545812606812), (' Latin', 0.999841570854187), ('.\n', 0.977022647857666), ('What', 0.9241418242454529), (' was', 0.9933071732521057), ('chu', 1.0), (' was', 0.999841570854187), (' general', 0.9999998807907104), (' and', 1.0), (' general', 1.0), ('.', 0.9980732202529907), ('ules', 1.0)]</t>
         </is>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -481,12 +481,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, United StatesThe</t>
+          <t>Hamilton, Ontario, CanadaYes, you can</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[(' St', 0.333251953125), (',', 1.0), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0)]</t>
+          <t>[(' St', 0.067626953125), (',', 0.85205078125), (' Louis', 0.5029296875), ('&lt;/s&gt;', 0.93994140625), ('The', 0.34326171875), ('&lt;/s&gt;', 0.97705078125), ('The', 0.36083984375), (' first', 0.11029052734375), (' you', 0.2159423828125), (' can', 0.80615234375)]</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, United StatesA few years ago, I had the privilege of attending a meeting of the National</t>
+          <t>St. Louis, MissouriYes, it is true. But it is also true that it is not the same as the</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[(' St', 0.333251953125), ('.', 1.0), (' Louis', 1.0), ('&lt;/s&gt;', 0.99951171875), ('The', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.92431640625), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.9931640625), (' time', 0.9931640625), (' students', 0.92431640625), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.92431640625), (' visit', 0.9931640625), (' visit', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.9931640625), (' group', 0.99365234375), (' the', 1.0), (' National', 0.9931640625)]</t>
+          <t>[(' St', 0.067626953125), ('.', 0.98193359375), (' Louis', 0.5029296875), ('&lt;/s&gt;', 0.93994140625), ('The', 0.34326171875), ('&lt;/s&gt;', 0.97705078125), ('The', 0.36083984375), (' first', 0.11029052734375), (' you', 0.2159423828125), (' can', 0.87255859375), (' use', 0.2078857421875), (' lot', 0.1829833984375), (' same', 0.311279296875), (' only', 0.09027099609375), (' different', 0.484619140625), (' not', 0.5078125), (' true', 0.410400390625), (' that', 0.98193359375), (' the', 0.3173828125), (' majority', 0.0863037109375), (' not', 0.38134765625), (' a', 0.169189453125), (' only', 0.417724609375), (' find', 0.1973876953125), (' the', 0.5458984375)]</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>computer science and artificial intelligenceA few years ago</t>
+          <t>Computational complexity theory&lt;!DOCTYPE html&gt;</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[(' computer', 0.99951171875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99951171875), ('The', 1.0), ('The', 1.0), (' first', 1.0), (' time', 0.9931640625), (' saw', 0.99951171875)]</t>
+          <t>[(' computer', 0.50439453125), (' science', 0.962890625), ('&lt;/s&gt;', 0.95263671875), ('The', 0.223388671875), ('The', 0.211669921875), ('The', 0.2293701171875), (' first', 0.123046875), ('php', 0.93994140625), ('\n', 0.3203125), ('\n', 0.90478515625)]</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>computer science and artificial intelligenceA few years ago, I had the privilege of attending a meeting of the International Society for the</t>
+          <t>Computational complexity theory&lt;font color="#666666" size="-2" face="verdana,arial,helvetica,sans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[(' computer', 0.99951171875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99951171875), ('The', 1.0), ('The', 1.0), (' first', 1.0), (' time', 0.9931640625), (' saw', 0.99951171875), (',', 1.0), (' I', 0.99951171875), (' was', 1.0), (' in', 0.9931640625), (' conversation', 0.9931640625), (' of', 1.0), (' meet', 0.92431640625), (' a', 0.9931640625), (' meeting', 0.92431640625), (' group', 0.99951171875), (' the', 1.0), (' International', 0.92431640625), (' Society', 0.92431640625), (' the', 1.0), (' Comput', 0.92431640625)]</t>
+          <t>[(' computer', 0.50439453125), (' science', 0.962890625), ('&lt;/s&gt;', 0.95263671875), ('The', 0.223388671875), ('The', 0.211669921875), ('The', 0.2293701171875), (' first', 0.123046875), (' is', 0.394775390625), (' of', 0.1932373046875), ('red', 0.3583984375), ('66', 0.96240234375), ('"&gt;', 0.85205078125), (' &lt;', 0.1353759765625), ('3"&gt;', 0.2578125), ('A', 0.10614013671875), (' &lt;', 0.2369384765625), ('verd', 0.92431640625), ('bold', 0.93994140625), ('"&gt;', 0.56201171875), ('arial', 0.880859375), (',', 0.880859375), ('hel', 0.90478515625), ('vetica', 0.99755859375), (',', 0.92431640625), ('sans', 0.73095703125)]</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 0.998046875), (' first', 1.0), (' first', 0.99951171875), (' ago', 1.0), (',', 1.0), (' I', 0.99951171875), (' was', 0.99951171875), (' in', 0.9931640625)]</t>
+          <t>[(' French', 0.5791015625), ('&lt;/s&gt;', 0.95263671875), ('The', 0.2166748046875), (' first', 0.143798828125), (' first', 0.130859375), (' ago', 0.880859375), (',', 0.76611328125), (' I', 0.393798828125), (' &lt;', 0.09991455078125), (' in', 0.13525390625)]</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FrenchA few years ago, I was in a relationship with a man I had a crush on for a long time.</t>
+          <t>FrenchIn the United States of America, there are more than 200,000 people who are deaf or hard of hearing.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 0.998046875), (' first', 1.0), (' first', 0.99951171875), (' ago', 1.0), (',', 1.0), (' I', 0.99951171875), (' was', 0.99951171875), (' in', 0.9931640625), (' very', 0.5), (' to', 1.0), (' meet', 0.5), (' a', 0.9931640625), (' meeting', 0.9931640625), (' who', 0.92431640625), (' was', 0.9931640625), (' International', 0.9931640625), (' crush', 1.0), (' He', 0.99951171875), (' for', 0.9931640625), (' a', 1.0), (' long', 0.923828125), (' time', 1.0), ('.', 1.0)]</t>
+          <t>[(' French', 0.5791015625), ('&lt;/s&gt;', 0.95263671875), ('The', 0.2166748046875), (' first', 0.143798828125), (' United', 0.119140625), (' large', 0.1500244140625), (',', 0.85205078125), (' the', 0.6064453125), (' United', 0.2169189453125), (' the', 0.58056640625), (' United', 0.2490234375), (' over', 0.1409912109375), (' 1', 0.1363525390625), (' 1', 0.103515625), ('000', 0.30712890625), (' people', 0.2481689453125), (' registered', 0.1815185546875), (' registered', 0.1368408203125), (' people', 0.341552734375), (' the', 0.410400390625), ('.', 0.62841796875), ('&lt;/s&gt;', 0.1629638671875), (' of', 0.90478515625), (' hearing', 0.9931640625), ('.', 0.69140625)]</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[(' Richmond', 0.8740234375), (',', 0.8994140625), ('e', 1.0), (',', 1.0), (' Ontario', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.84814453125), ('The', 1.0), (' first', 0.6513671875)]</t>
+          <t>[(' Richmond', 0.09759521484375), ('co', 0.99951171875), ('e', 0.99853515625), (',', 0.767578125), (' Ontario', 0.5400390625), ('&lt;/s&gt;', 0.92822265625), ('The', 0.380615234375), (' first', 0.12139892578125), ('The', 0.371826171875), (' first', 0.1239013671875)]</t>
         </is>
       </c>
     </row>
@@ -691,13 +691,13 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simcoe, OntarioI. INTRODUCTION
-In recent years, there has been a growing interest in the</t>
+          <t>Richmond, VirginiaI. INTRODUCTION
+In recent years, there has been a growing interest in the use of</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[(' Richmond', 0.8740234375), (',', 0.8994140625), ('e', 1.0), (',', 1.0), (' Ontario', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.84814453125), ('The', 1.0), (' first', 0.6513671875), ('DU', 1.0), ('CTION', 1.0), ('\n', 1.0), ('The', 1.0), (' discovery', 0.5546875), ('The', 1.0), (',', 1.0), (' the', 0.9990234375), (' use', 0.84814453125), (' been', 1.0), (' a', 0.99853515625), (' growing', 1.0), (' interest', 1.0), (' in', 1.0), (' the', 1.0)]</t>
+          <t>[(' Richmond', 0.09759521484375), (',', 0.5546875), (' Virginia', 0.4248046875), ('&lt;/s&gt;', 0.98828125), ('The', 0.3876953125), (' first', 0.1324462890625), ('The', 0.380859375), (' first', 0.12841796875), ('DU', 0.99755859375), ('CTION', 0.99951171875), ('\n', 0.98583984375), ('The', 0.466064453125), (' study', 0.10076904296875), (' years', 0.9033203125), (',', 0.91845703125), (' the', 0.42822265625), (' use', 0.15576171875), (' been', 0.99462890625), (' a', 0.6162109375), (' growing', 0.34521484375), (' interest', 0.97265625), (' in', 0.9921875), (' the', 0.72705078125), (' use', 0.2998046875), (' of', 0.99462890625)]</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>computer scienceI. INTRODUCTION</t>
+          <t>Computer scienceThis is not a review.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[(' computer', 0.7607421875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' INT', 1.0), ('RO', 1.0), ('DU', 1.0), ('CTION', 1.0), ('\n', 1.0)]</t>
+          <t>[(' computer', 0.2861328125), (' science', 0.91357421875), ('&lt;/s&gt;', 0.98095703125), ('The', 0.330078125), (' first', 0.1314697265625), (' a', 0.50048828125), (' great', 0.2060546875), (' review', 0.185791015625), (' all', 0.377685546875), (' the', 0.490478515625)]</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[(' computer', 0.7607421875), (' science', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' INT', 1.0), ('RO', 1.0), ('DU', 1.0), ('CTION', 1.0), ('\n', 1.0), ('The', 1.0), (' discovery', 0.77734375), (' last', 0.9345703125), (',', 1.0), (' the', 0.99951171875), (' development', 0.79296875), (' been', 1.0), (' a', 0.9990234375), (' growing', 1.0), (' interest', 1.0), (' in', 1.0), (' the', 1.0), (' use', 0.88427734375), (' of', 1.0), (' artificial', 0.98291015625)]</t>
+          <t>[(' computer', 0.2861328125), (' science', 0.91357421875), ('&lt;/s&gt;', 0.98095703125), ('The', 0.330078125), (' first', 0.1314697265625), (' INT', 0.9296875), ('RO', 1.0), ('DU', 0.99560546875), ('CTION', 0.99951171875), ('\n', 0.98583984375), ('The', 0.463134765625), (' discovery', 0.1126708984375), (' last', 0.3681640625), (',', 0.921875), (' the', 0.424072265625), (' consider', 0.2445068359375), (' been', 0.99365234375), (' a', 0.61474609375), (' growing', 0.344482421875), (' interest', 0.97607421875), (' in', 0.99169921875), (' the', 0.74365234375), (' use', 0.269775390625), (' of', 0.994140625), (' artificial', 0.156005859375)]</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FrenchI am not sure if this is a</t>
+          <t>FrenchI. INTRODUCTION
+The</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' been', 0.55810546875), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125)]</t>
+          <t>[(' French', 0.83837890625), ('&lt;/s&gt;', 0.99169921875), ('The', 0.31689453125), (' first', 0.1458740234375), (' a', 0.5107421875), ('RO', 1.0), ('DU', 0.99609375), ('CTION', 0.99951171875), ('\n', 0.98681640625), ('The', 0.449951171875)]</t>
         </is>
       </c>
     </row>
@@ -813,12 +814,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FrenchI am not sure if this is the right place to ask this question, but what is the best title for this</t>
+          <t>FrenchI am going to try to keep it simple. I am going to try to keep it simple. I am going</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[(' French', 1.0), ('&lt;/s&gt;', 1.0), ('The', 1.0), (' first', 0.99560546875), (' been', 0.55810546875), (' a', 0.77734375), (' if', 1.0), (' is', 0.947265625), (' the', 1.0), (' a', 0.9736328125), (' good', 1.0), (' place', 1.0), (' to', 1.0), (' ask', 1.0), (' this', 0.99951171875), (',', 0.92431640625), (' is', 0.7490234375), (' is', 0.98046875), (' is', 0.59619140625), (' a', 0.9990234375), (' way', 1.0), (' way', 1.0), (' get', 0.99658203125), (' the', 1.0), (' city', 0.615234375)]</t>
+          <t>[(' French', 0.83837890625), ('&lt;/s&gt;', 0.99169921875), ('The', 0.31689453125), (' first', 0.1458740234375), (' a', 0.2978515625), (' student', 0.100341796875), (' get', 0.1517333984375), (' a', 0.363037109375), (' keep', 0.145263671875), (' this', 0.4638671875), (' short', 0.2484130859375), ('.', 0.4462890625), (' I', 0.50537109375), (' am', 0.4140625), (' going', 0.360107421875), (' I', 0.368896484375), (' try', 0.138916015625), (' to', 0.8935546875), (' keep', 0.3515625), (' it', 0.70068359375), (' simple', 0.2325439453125), ('.', 0.95654296875), ('&lt;/s&gt;', 0.673828125), ('The', 0.370849609375), (' going', 0.9970703125)]</t>
         </is>
       </c>
     </row>
@@ -843,12 +844,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The location of being the location of being the location</t>
+          <t>What is the location of Simcoe Compos.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[('\n', 0.9056810140609741), ('The', 0.999806821346283), ('of', 0.9999998807907104), ('Sim', 0.8489604592323303), ('The', 0.9926338791847229), ('location', 0.9999997615814209), ('.', 0.9669291377067566), ('being', 1.0), ('the', 1.0), ('location', 1.0)]</t>
+          <t>[('\n', 0.16284143924713135), ('location', 0.8768665790557861), ('of', 0.7782554030418396), ('Sim', 0.21301856637001038), ('of', 0.9516806602478027), ('Sim', 0.6061411499977112), ('co', 0.7831542491912842), ('e', 0.517654299736023), ('Compos', 0.5809311866760254), ('.', 0.32017552852630615)]</t>
         </is>
       </c>
     </row>
@@ -873,12 +874,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The location of being a a a a a a a a a a a a a a a a a a a a a</t>
+          <t>What is the location of Simcoe Com.
+This entry was posted in Uncategorized and tagged 2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[('\n', 0.9056810140609741), ('The', 0.999806821346283), ('of', 0.9999998807907104), ('Sim', 0.8489604592323303), ('The', 0.9926338791847229), ('location', 0.9999997615814209), ('.', 0.9669291377067566), ('being', 1.0), ('the', 1.0), ('location', 1.0), ('of', 1.0), ('being', 1.0), ('the', 1.0), ('location', 1.0), ('of', 1.0), ('being', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0), ('a', 1.0)]</t>
+          <t>[('\n', 0.16284143924713135), ('The', 0.15345986187458038), ('of', 0.7782554030418396), ('Sim', 0.21301856637001038), ('of', 0.9516806602478027), ('Sim', 0.6061411499977112), ('co', 0.7831542491912842), ('e', 0.517654299736023), ('Compos', 0.5809311866760254), ('.', 0.32017552852630615), ('\n', 0.36472463607788086), ('The', 0.18296994268894196), ('is', 0.5279859304428101), ('a', 0.5976619124412537), ('list', 0.2745484709739685), ('in', 0.8320504426956177), ('Un', 0.3747318387031555), ('c', 0.9997830986976624), ('ategor', 0.9998750686645508), ('ized', 0.9789106249809265), ('and', 0.5076173543930054), ('tag', 0.9999611377716064), ('ged', 0.9999743700027466), ('', 0.41763293743133545), ('2', 0.474136084318161)]</t>
         </is>
       </c>
     </row>
@@ -908,7 +910,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[('Alan', 0.9705228209495544), ('T', 0.9999983310699463), ('uring', 1.0), ('was', 0.9998005032539368), ('a', 0.9999997615814209), ('British', 0.9999994039535522), ('of', 1.0), ('expert', 1.0), ('ise', 1.0), ('was', 0.5156328082084656)]</t>
+          <t>[('Alan', 0.3571459650993347), ('T', 0.6497820615768433), ('uring', 0.9843579530715942), ('was', 0.49879613518714905), ('a', 0.7125629782676697), ('British', 0.4992287755012512), ('of', 0.9968804121017456), ('expert', 0.9915937185287476), ('ise', 0.997665286064148), ('was', 0.4472676217556)]</t>
         </is>
       </c>
     </row>
@@ -933,12 +935,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alan Turing was a British mathematician and computer scientist. Alan Turing was a British mathematician and computer</t>
+          <t>Alan Turing was a British mathematician and computer scientist. He is best known for his work on the Turing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[('Alan', 0.9705228209495544), ('T', 0.9999983310699463), ('uring', 1.0), ('was', 0.9998005032539368), ('a', 0.9999997615814209), ('British', 0.9999994039535522), ('of', 1.0), ('expert', 1.0), ('ise', 1.0), ('was', 0.5156328082084656), ('in', 0.9886047840118408), ('scient', 0.9999862909317017), ('ist', 1.0), ('who', 0.9482312202453613), ('was', 0.5188665986061096), ('a', 0.9923862218856812), ('uring', 1.0), ('was', 0.9999997615814209), ('a', 0.9105008244514465), ('work', 0.9991388320922852), ('on', 0.9998329877853394), ('ematic', 1.0), ('ian', 1.0), ('and', 1.0), ('computer', 1.0)]</t>
+          <t>[('Alan', 0.3571459650993347), ('T', 0.6497820615768433), ('uring', 0.9843579530715942), ('was', 0.49879613518714905), ('a', 0.7125629782676697), ('British', 0.4992287755012512), ('of', 0.9968804121017456), ('expert', 0.9915937185287476), ('ise', 0.997665286064148), ('was', 0.4472676217556), ('in', 0.22544877231121063), ('scient', 0.6062339544296265), ('ist', 0.9932287931442261), ('who', 0.5164232850074768), ('was', 0.24916724860668182), ('best', 0.21608109772205353), ('was', 0.4129793047904968), ('born', 0.3532226085662842), ('for', 0.9166389107704163), ('his', 0.9606783986091614), ('work', 0.6253705620765686), ('on', 0.7377659678459167), ('the', 0.8201623558998108), ('T', 0.9546257853507996), ('uring', 0.9805128574371338)]</t>
         </is>
       </c>
     </row>
@@ -963,12 +965,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The native language of Louis Jules Trochu is</t>
+          <t>Louis Jules Trochu was born in 1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[('Louis', 0.9989312291145325), ('Jules', 0.9602460861206055), ('Tro', 1.0), ('ch', 1.0), ('u', 1.0), ('was', 0.9966222047805786), ('born', 0.9999992847442627), ('on', 0.9376497864723206), ('u', 1.0), ('is', 1.0)]</t>
+          <t>[('Louis', 0.32439568638801575), ('Jules', 0.5789459943771362), ('Tro', 0.995751142501831), ('ch', 0.9873861074447632), ('u', 0.9978564381599426), ('was', 0.4595409631729126), ('was', 0.5887033939361572), ('born', 0.6867790818214417), ('on', 0.5561119318008423), ('', 0.376668244600296)]</t>
         </is>
       </c>
     </row>
@@ -993,13 +995,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The native language of Louis Jules Trochu is French.
-Louis Jules Trochu was born in 184</t>
+          <t>What is the native language of Louis Jules Trochu? What is the native language of Louis Jules Trochu? What</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[('Louis', 0.9989312291145325), ('Jules', 0.9602460861206055), ('Tro', 1.0), ('ch', 1.0), ('u', 1.0), ('was', 0.9966222047805786), ('born', 0.9999992847442627), ('on', 0.9376497864723206), ('u', 1.0), ('is', 1.0), ('French', 1.0), ('.', 1.0), ('Louis', 0.9999943971633911), ('Jules', 0.9775069952011108), ('Tro', 1.0), ('ch', 1.0), ('u', 1.0), ('was', 0.9996870756149292), ('was', 0.9999982118606567), ('on', 0.9999995231628418), ('', 0.9202308058738708), ('', 0.9996960163116455), ('1', 0.8204210996627808), ('4', 0.5435603857040405), ('4', 0.6353700757026672)]</t>
+          <t>[('Louis', 0.32439568638801575), ('Jules', 0.5789459943771362), ('Tro', 0.995751142501831), ('ch', 0.9873861074447632), ('u', 0.9978564381599426), ('was', 0.4595409631729126), ('was', 0.5887033939361572), ('born', 0.6867790818214417), ('on', 0.5561119318008423), ('', 0.376668244600296), ('u', 0.9977043271064758), ('?', 0.9922194480895996), ('What', 0.29424384236335754), ('is', 0.9796625971794128), ('the', 0.9856573343276978), ('native', 0.9752694964408875), ('language', 0.9981659054756165), ('of', 0.9967978596687317), ('Louis', 0.9982815980911255), ('Jules', 0.9381629228591919), ('Tro', 0.9993552565574646), ('ch', 0.999394416809082), ('u', 0.9993355870246887), ('?', 0.9977178573608398), ('What', 0.9174103736877441)]</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 0.9999998807907104), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0)]</t>
+          <t>[('&lt;/s&gt;', 0.7931222915649414), ('', 0.9999573230743408), ('\n', 0.9999954700469971), ('&lt;', 0.9914224743843079), ('|', 0.9999798536300659), ('ass', 0.9991958737373352), ('istant', 0.9999822378158569), ('|', 0.999841570854187), ('&gt;', 0.9999966621398926), ('\n', 0.9999517202377319)]</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1061,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 0.9999998807907104), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0), ('The', 0.9933071732521057), ('location', 1.0), ('of', 1.0), ('Sim', 1.0), ('co', 1.0), ('e', 1.0), ('Compos', 1.0), ('ite', 1.0), ('School', 1.0), ('is', 1.0), ('', 1.0), ('1', 0.9994471669197083), ('0', 0.977022647857666), ('1', 0.9994471669197083), ('0', 0.977022647857666)]</t>
+          <t>[('&lt;/s&gt;', 0.7931222915649414), ('', 0.9999573230743408), ('\n', 0.9999954700469971), ('&lt;', 0.9914224743843079), ('|', 0.9999798536300659), ('ass', 0.9991958737373352), ('istant', 0.9999822378158569), ('|', 0.999841570854187), ('&gt;', 0.9999966621398926), ('\n', 0.9999517202377319), ('The', 0.622459352016449), ('location', 0.9362850189208984), ('of', 0.9970190525054932), ('Sim', 0.9988304972648621), ('co', 0.9999979734420776), ('e', 0.9999998807907104), ('Compos', 0.9999904632568359), ('ite', 0.999995231628418), ('School', 0.9975274205207825), ('is', 0.949669361114502), ('', 0.8933094143867493), ('1', 0.4202403724193573), ('0', 0.23686398565769196), ('1', 0.4399493634700775), ('0', 0.23922346532344818)]</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 1.0), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0)]</t>
+          <t>[('&lt;/s&gt;', 0.9099069833755493), ('', 0.9999785423278809), ('\n', 0.9999980926513672), ('&lt;', 0.9928786158561707), ('|', 0.9999097585678101), ('ass', 0.9989677667617798), ('istant', 0.9999822378158569), ('|', 0.9996199607849121), ('&gt;', 0.9999986886978149), ('\n', 0.999993085861206)]</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1122,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 1.0), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0), ('Al', 1.0), ('an', 1.0), ('T', 1.0), ('uring', 1.0), ("'", 0.9933071732521057), ('s', 1.0), ('area', 1.0), ('of', 1.0), ('expert', 1.0), ('ise', 1.0), ('was', 0.9980732202529907), ('theoretical', 1.0), ('computer', 1.0), ('science', 1.0), (',', 0.7772998809814453)]</t>
+          <t>[('&lt;/s&gt;', 0.9099069833755493), ('', 0.9999785423278809), ('\n', 0.9999980926513672), ('&lt;', 0.9928786158561707), ('|', 0.9999097585678101), ('ass', 0.9989677667617798), ('istant', 0.9999822378158569), ('|', 0.9996199607849121), ('&gt;', 0.9999986886978149), ('\n', 0.999993085861206), ('Al', 0.9796676635742188), ('an', 0.9994471669197083), ('T', 0.9997040629386902), ('uring', 0.9999926090240479), ("'", 0.622459352016449), ('s', 0.999996542930603), ('area', 0.9840936064720154), ('of', 0.9999861717224121), ('expert', 0.9997546076774597), ('ise', 0.9999946355819702), ('was', 0.6513549089431763), ('theoretical', 0.7471963167190552), ('computer', 0.9648551344871521), ('science', 0.9994115829467773), (',', 0.531209409236908)]</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1152,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 1.0), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0)]</t>
+          <t>[('&lt;/s&gt;', 0.9433475732803345), ('', 0.999987006187439), ('\n', 0.9999966621398926), ('&lt;', 0.9953904151916504), ('|', 0.9998910427093506), ('ass', 0.9982993006706238), ('istant', 0.9999756813049316), ('|', 0.9999904632568359), ('&gt;', 0.9999985694885254), ('\n', 0.9999910593032837)]</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1183,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[('&lt;/s&gt;', 1.0), ('', 1.0), ('\n', 1.0), ('&lt;', 1.0), ('|', 1.0), ('ass', 1.0), ('istant', 1.0), ('|', 1.0), ('&gt;', 1.0), ('\n', 1.0), ('The', 1.0), ('native', 1.0), ('language', 1.0), ('of', 1.0), ('Louis', 1.0), ('Jules', 1.0), ('Tro', 1.0), ('ch', 1.0), ('u', 1.0), ('is', 1.0), ('French', 1.0), ('.', 1.0), ('&lt;/s&gt;', 1.0), ('', 1.0), ('\n', 1.0)]</t>
+          <t>[('&lt;/s&gt;', 0.9433475732803345), ('', 0.999987006187439), ('\n', 0.9999966621398926), ('&lt;', 0.9953904151916504), ('|', 0.9998910427093506), ('ass', 0.9982993006706238), ('istant', 0.9999756813049316), ('|', 0.9999904632568359), ('&gt;', 0.9999985694885254), ('\n', 0.9999910593032837), ('The', 0.8670357465744019), ('native', 0.9970190525054932), ('language', 0.9999251365661621), ('of', 0.9978172779083252), ('Louis', 0.9986749291419983), ('Jules', 0.9994115829467773), ('Tro', 0.9999852180480957), ('ch', 0.999998927116394), ('u', 0.9999979734420776), ('is', 0.9399133324623108), ('French', 0.977022647857666), ('.', 0.957912266254425), ('&lt;/s&gt;', 0.9399133324623108), ('', 0.9999982118606567), ('\n', 0.9999985694885254)]</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1213,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[(' Sim', 0.9999151229858398), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 0.999998927116394), (' at', 0.977022647857666), (' ', 1.0), ('1', 0.977022647857666), (',', 1.0)]</t>
+          <t>[(' Sim', 0.3305044174194336), ('coe', 0.9991958737373352), (' Composite', 0.9046505093574524), (' School', 0.9820137619972229), (' is', 0.9669140577316284), (' located', 0.7981867790222168), (' at', 0.5926666259765625), (' ', 0.9796676635742188), ('1', 0.07397094368934631), (',', 0.9626730680465698)]</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1238,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Where is Simcoe Composite School located?
-Simcoe Composite School is located in Simcoe, Ontario, Canada.
-What is the</t>
+          <t>What is the location of Simcoe Composite School?
+What is the location of Simcoe Composite School?
+Simcoe Composite School is</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[(' Sim', 0.9999151229858398), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 0.999998927116394), (' at', 0.977022647857666), (' ', 1.0), ('1', 0.977022647857666), (',', 1.0), (' Ontario', 1.0), ('.', 0.7772998809814453), (' The', 0.9875683188438416), ('.', 0.9241418242454529), (' in', 0.5), (' Sim', 0.999998927116394), ('1', 0.9241418242454529), (',', 1.0), (' Ontario', 0.9999998807907104), (',', 0.5), (' Canada', 1.0), ('.', 0.7773000597953796), (' The', 0.9241418838500977), (' is', 0.9999998807907104), (' the', 1.0)]</t>
+          <t>[(' Sim', 0.3305044174194336), ('coe', 0.9991958737373352), (' Composite', 0.9046505093574524), (' School', 0.9820137619972229), (' is', 0.9669140577316284), (' located', 0.7981867790222168), (' at', 0.5926666259765625), (' ', 0.9796676635742188), ('1', 0.07397094368934631), (',', 0.9626730680465698), (' Ontario', 0.8807970285415649), ('.', 0.3891374468803406), (' The', 0.2783873975276947), (' School', 0.9820137619972229), (' is', 0.9669140577316284), (' located', 0.9241418242454529), (' at', 0.6791787147521973), (' Composite', 0.9981897473335266), (' School', 0.9996199607849121), ('?\n', 0.8354835510253906), ('Sim', 0.500963032245636), ('coe', 0.9992903470993042), (' Composite', 0.9755768775939941), (' School', 0.977022647857666), (' is', 0.957912266254425)]</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1270,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The Imitation Game is a 2014</t>
+          <t>What is Alan Turing's area of expertise? What</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' I', 0.9964063763618469), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398)]</t>
+          <t>[(' The', 0.13540858030319214), (' is', 0.5889215469360352), (' was', 0.2655467391014099), (' name', 0.36704376339912415), ("'s", 0.9740425944328308), (' area', 0.9626730680465698), (' of', 0.9992903470993042), (' expertise', 0.9908744096755981), ('?', 0.6791787147521973), (' What', 0.3666400611400604)]</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1300,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The Imitation Game (2014) cast and crew credits, including actors, actresses, directors, writers and more.</t>
+          <t>What is Alan Turing's area of expertise? What is Alan Turing's area of expertise? What is Alan Turing's area of</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[(' The', 0.5), (' is', 0.9999998807907104), (' the', 0.6513549089431763), (' name', 0.9999998807907104), ("'s", 1.0), (' is', 0.9989677667617798), (' of', 1.0), (' expertise', 1.0), ('?', 0.9994471669197083), (' What', 0.9999151229858398), (' British', 0.9241418242454529), (' Alan', 1.0), (' Turing', 1.0), ("'s", 1.0), (' area', 1.0), (' of', 1.0), (' expertise', 1.0), ('?', 0.9999963045120239), (' What', 1.0), (' directors', 1.0), (',', 1.0), (' writers', 1.0), (' and', 1.0), (' more', 1.0), ('.', 1.0)]</t>
+          <t>[(' The', 0.13540858030319214), (' is', 0.5889215469360352), (' was', 0.2655467391014099), (' name', 0.36704376339912415), ("'s", 0.9740425944328308), (' area', 0.9626730680465698), (' of', 0.9992903470993042), (' expertise', 0.9908744096755981), ('?', 0.6791787147521973), (' What', 0.3666400611400604), (' is', 0.949669361114502), (' Alan', 0.8933094143867493), (' Turing', 0.9995417594909668), ("'s", 0.9902915358543396), (' area', 0.9944451451301575), (' of', 0.999480664730072), (' expertise', 0.9975274205207825), ('?', 0.7772998809814453), (' What', 0.8991213440895081), (' is', 0.9914224743843079), (' Alan', 0.9724147915840149), (' Turing', 0.9979493021965027), ("'s", 0.9971990585327148), (' area', 0.9981897473335266), (' of', 0.9992903470993042)]</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1335,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[(' What', 0.9964063763618469), (' is', 0.9999994039535522), (' the', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.977022647857666), (' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0)]</t>
+          <t>[(' What', 0.2057133913040161), (' is', 0.7189714312553406), (' the', 0.9324532747268677), (' Tro', 0.999929666519165), ('chu', 0.9940890073776245), (' was', 0.35851407051086426), (' Louis', 0.7864826321601868), (' J', 0.9755768775939941), ('ules', 0.9970190525054932), (' Tro', 0.9998910427093506)]</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1366,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[(' What', 0.9964063763618469), (' is', 0.9999994039535522), (' the', 1.0), (' Tro', 1.0), ('chu', 1.0), (' was', 0.977022647857666), (' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0), ('?\n', 0.9994471669197083), ('Latin', 0.5), (' J', 1.0), ('�', 1.0), ('yl', 1.0), (' t', 0.9999963045120239), (' was', 0.9989677667617798), ('�', 1.0), ('oku', 1.0), (' Louis', 1.0), (' J', 1.0), ('ules', 1.0), (' Tro', 1.0), ('chu', 1.0)]</t>
+          <t>[(' What', 0.2057133913040161), (' is', 0.7189714312553406), (' the', 0.9324532747268677), (' Tro', 0.999929666519165), ('chu', 0.9940890073776245), (' was', 0.35851407051086426), (' Louis', 0.7864826321601868), (' J', 0.9755768775939941), ('ules', 0.9970190525054932), (' Tro', 0.9998910427093506), ('chu', 0.9997695088386536), ('?\n', 0.6791787147521973), ('Latin', 0.2535788416862488), (' J', 0.9626730680465698), ('�', 0.9995121955871582), ('yl', 0.9947799444198608), (' t', 0.7772998809814453), (' was', 0.3887117803096771), ('�', 0.9964063763618469), ('oku', 0.9149009585380554), (' Louis', 0.9859364032745361), (' J', 0.9933071732521057), ('ules', 0.999841570854187), (' Tro', 0.9998910427093506), ('chu', 0.9998910427093506)]</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1396,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[(' Sim', 0.9999996423721313), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.999841570854187), (' Sim', 1.0), ('coe', 1.0), (',', 1.0)]</t>
+          <t>[(' Sim', 0.8175744414329529), ('coe', 0.9999946355819702), (' Composite', 0.999373733997345), (' School', 0.9996199607849121), (' is', 0.9953904151916504), (' located', 0.9046505093574524), (' in', 0.7057850360870361), (' Sim', 0.9362850189208984), ('coe', 0.9999852180480957), (',', 0.9971990585327148)]</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1426,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>[(' Sim', 0.9999996423721313), ('coe', 1.0), (' Composite', 1.0), (' School', 1.0), (' is', 1.0), (' located', 1.0), (' in', 0.999841570854187), (' Sim', 1.0), ('coe', 1.0), (',', 1.0), (' Ontario', 1.0), (',', 1.0), (' Canada', 1.0), ('.', 0.9933071732521057), (' It', 0.9241418242454529), (' is', 1.0), (' the', 1.0), (' location', 0.9980732202529907), (' high', 0.7772998809814453), (' the', 1.0), (' heart', 1.0), (' of', 1.0), (' Sim', 0.9241418242454529), ('coe', 1.0), (',', 1.0)]</t>
+          <t>[(' Sim', 0.8175744414329529), ('coe', 0.9999946355819702), (' Composite', 0.999373733997345), (' School', 0.9996199607849121), (' is', 0.9953904151916504), (' located', 0.9046505093574524), (' in', 0.7057850360870361), (' Sim', 0.9362850189208984), ('coe', 0.9999852180480957), (',', 0.9971990585327148), (' Ontario', 0.9875683188438416), (',', 0.9525741338729858), (' Canada', 0.9796676635742188), ('.', 0.622459352016449), (' It', 0.4995177388191223), (' is', 0.8807970285415649), (' the', 0.9975274205207825), (' location', 0.20481885969638824), (' high', 0.531209409236908), (' the', 0.9914224743843079), (' heart', 0.9937100410461426), (' of', 0.999373733997345), (' Sim', 0.562176525592804), ('coe', 0.9999599456787109), (',', 0.9149009585380554)]</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1451,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>A) Computer Science B) Mathematics C) Physics</t>
+          <t>Alan Turing was a British mathematician, computer scientist</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[(' A', 0.9994471669197083), (')', 0.9933071732521057), (' Computer', 0.9999545812606812), (' Science', 0.9999996423721313), (' B', 1.0), (')', 1.0), (' Mathematics', 0.999841570854187), (' C', 1.0), (')', 1.0), (' Physics', 0.9933071732521057)]</t>
+          <t>[(' A', 0.30556392669677734), (')', 0.622459352016449), (' Computer', 0.35304179787635803), (' Science', 0.8175744414329529), (' B', 0.8670357465744019), (')', 0.9982993006706238), (' Mathematics', 0.48907434940338135), (',', 0.9149009585380554), (' computer', 0.9859364032745361), (' scientist', 0.9992903470993042)]</t>
         </is>
       </c>
     </row>
@@ -1480,14 +1481,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>A) Computer Science B) Mathematics C) Physics D) Biology
-Answer: A) Computer Science
-Explanation: Alan Turing</t>
+          <t>Alan Turing is a renowned mathematician, computer scientist, and logician who made significant contributions to the development of computer science,</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>[(' A', 0.9994471669197083), (')', 0.9933071732521057), (' Computer', 0.9999545812606812), (' Science', 0.9999996423721313), (' B', 1.0), (')', 1.0), (' Mathematics', 0.999841570854187), (' C', 1.0), (')', 1.0), (' Physics', 0.9933071732521057), (' D', 1.0), (')', 1.0), (' Biology', 0.999987006187439), ('\n', 0.999998927116394), ('Answer', 0.9999998807907104), (':', 1.0), (' A', 1.0), (')', 1.0), (' Computer', 1.0), (' Science', 1.0), ('\n', 1.0), ('Explanation', 0.9994471669197083), (':', 1.0), (' Alan', 1.0), (' Turing', 1.0)]</t>
+          <t>[(' A', 0.30556392669677734), (')', 0.622459352016449), (' Computer', 0.35304179787635803), (' Science', 0.8175744414329529), (' B', 0.8670357465744019), (')', 0.9982993006706238), (' Mathematics', 0.48907434940338135), (' computer', 0.5178173184394836), (')', 0.9991958737373352), (' Physics', 0.3324020206928253), (' mathematics', 0.9399133324623108), ('.', 0.5926666259765625), (' He', 0.7981867790222168), ('ian', 0.9998089671134949), ('.', 0.7057850360870361), (' fields', 0.851952850818634), (' of', 0.9998089671134949), (' artificial', 0.7893977761268616), (' intelligence', 0.9995121955871582), (',', 0.9525741338729858), (' cryptography', 0.3995068371295929), ('Explanation', 0.6791787147521973), (' computer', 0.9840936064720154), (' science', 0.998498797416687), (',', 0.9399133324623108)]</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1511,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>What is the native language of Louis Jules Tro</t>
+          <t>Louis Jules Trochu was a French general and</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[(' Latin', 0.957912266254425), ('.\n', 0.9241418242454529), (' the', 1.0), (' native', 0.977022647857666), (' language', 1.0), (' of', 1.0), (' Louis', 1.0), (' of', 1.0), (' Louis', 1.0), (' Tro', 1.0)]</t>
+          <t>[(' Latin', 0.26305893063545227), ('.\n', 0.41246476769447327), ('ules', 0.9999966621398926), (' Tro', 0.9998910427093506), ('chu', 0.9995121955871582), (' was', 0.7042046189308167), (' a', 0.9324532747268677), (' French', 0.9956685304641724), (' general', 0.7981867790222168), (' and', 0.7310585379600525)]</t>
         </is>
       </c>
     </row>
@@ -1542,14 +1541,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Latin.
-What is the native language of Louis Jules Trochu? Latin.
+          <t>French.
+What is the native language of Louis Jules Trochu? French.
 What is the native language of Louis Jules</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[(' Latin', 0.957912266254425), ('.\n', 0.9241418242454529), (' the', 1.0), (' native', 0.977022647857666), (' language', 1.0), (' of', 1.0), (' Louis', 1.0), (' of', 1.0), (' Louis', 1.0), (' Tro', 1.0), ('chu', 1.0), ('?\n', 0.7772998809814453), ('chu', 1.0), ('?', 0.9999545812606812), (' Latin', 0.999841570854187), ('.\n', 0.977022647857666), ('What', 0.9241418242454529), (' was', 0.9933071732521057), ('chu', 1.0), (' was', 0.999841570854187), (' general', 0.9999998807907104), (' and', 1.0), (' general', 1.0), ('.', 0.9980732202529907), ('ules', 1.0)]</t>
+          <t>[(' Latin', 0.26305893063545227), ('.\n', 0.41246476769447327), ('ules', 0.9999966621398926), (' Tro', 0.9998910427093506), ('chu', 0.9995121955871582), (' was', 0.7042046189308167), (' a', 0.9324532747268677), (' French', 0.9956685304641724), (' general', 0.7981867790222168), (' and', 0.7310585379600525), (' politician', 0.9525741338729858), ('.', 0.4752510190010071), ('chu', 0.9999687671661377), ('?', 0.6791787147521973), (' French', 0.957912266254425), ('.\n', 0.531209409236908), (' and', 0.8354835510253906), (' was', 0.5544951558113098), ('.', 0.6513549089431763), (' native', 0.9362850189208984), (' general', 0.8354835510253906), (' of', 0.999373733997345), (' Louis', 0.8159579038619995), ('.\n', 0.562176525592804), ('What', 0.7057850360870361)]</t>
         </is>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandordaroczi/Documents/TUM/Masterarbeit/Python/quantization-reliability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBEA731-1617-B54D-859E-CC6A23260C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AFD578-D3AB-7947-B101-6568E55AE18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -309,6 +309,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
